--- a/employee_surveys/037_workplace_culture_evaluation_form--employee_surveys.xlsx
+++ b/employee_surveys/037_workplace_culture_evaluation_form--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1398,17 +1398,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_security_choices</t>
+          <t>company_culture_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>job_autonomy</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Job Autonomy</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1420,29 +1420,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>company_culture_choices</t>
+          <t>manager_leadership_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>bad</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bad</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>leadership</t>
+          <t>coaching</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>Coaching</t>
         </is>
       </c>
     </row>
@@ -1471,29 +1471,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>coaching</t>
+          <t>support</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Coaching</t>
+          <t>Support</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>manager_leadership_choices</t>
+          <t>team_morale_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>team_morale</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Team Morale</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>team_morale</t>
+          <t>engagement</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Team Morale</t>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
@@ -1522,29 +1522,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>engagement</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>Motivation</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>team_morale_choices</t>
+          <t>career_growth_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>motivation</t>
+          <t>career_growth</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Career Growth</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>career_growth</t>
+          <t>development</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Career Growth</t>
+          <t>Development</t>
         </is>
       </c>
     </row>
@@ -1573,29 +1573,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>opportunities</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Opportunities</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>career_growth_choices</t>
+          <t>company_values_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>opportunities</t>
+          <t>trust</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Opportunities</t>
+          <t>Trust</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>trust</t>
+          <t>integrity</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Trust</t>
+          <t>Integrity</t>
         </is>
       </c>
     </row>
@@ -1624,29 +1624,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>integrity</t>
+          <t>respect</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Integrity</t>
+          <t>Respect</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>company_values_2_choices</t>
+          <t>manager_support_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>respect</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Respect</t>
+          <t>Team Lead</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>team_lead</t>
+          <t>senior_manager</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Team Lead</t>
+          <t>Senior Manager</t>
         </is>
       </c>
     </row>
@@ -1675,29 +1675,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>senior_manager</t>
+          <t>director</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Senior Manager</t>
+          <t>Director</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>manager_support_2_choices</t>
+          <t>work_life_balance_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>director</t>
+          <t>formal</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Formal</t>
         </is>
       </c>
     </row>
@@ -1709,29 +1709,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>formal</t>
+          <t>informal</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Formal</t>
+          <t>Informal</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>work_life_balance_2_choices</t>
+          <t>team_morale_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>informal</t>
+          <t>team_morale</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Informal</t>
+          <t>Team Morale</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>team_morale</t>
+          <t>engagement</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Team Morale</t>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
@@ -1760,29 +1760,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>engagement</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>Motivation</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>team_morale_2_choices</t>
+          <t>job_security_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>motivation</t>
+          <t>job_security</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Job Security</t>
         </is>
       </c>
     </row>
@@ -1794,46 +1794,46 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>job_security</t>
+          <t>job_autonomy</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Job Security</t>
+          <t>Job Autonomy</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>job_security_2_choices</t>
+          <t>manager_leadership_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>job_autonomy</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Job Autonomy</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>job_security_2_choices</t>
+          <t>manager_leadership_2_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>job_autonomy</t>
+          <t>coaching</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Job Autonomy</t>
+          <t>Coaching</t>
         </is>
       </c>
     </row>
@@ -1845,46 +1845,46 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>leadership</t>
+          <t>support</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>Support</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>manager_leadership_2_choices</t>
+          <t>team_morale_3_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>coaching</t>
+          <t>team_morale</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Coaching</t>
+          <t>Team Morale</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>manager_leadership_2_choices</t>
+          <t>team_morale_3_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>engagement</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
@@ -1896,46 +1896,46 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>team_morale</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Team Morale</t>
+          <t>Motivation</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>team_morale_3_choices</t>
+          <t>career_growth_2_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>engagement</t>
+          <t>career_growth</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>Career Growth</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>team_morale_3_choices</t>
+          <t>career_growth_2_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>motivation</t>
+          <t>development</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Development</t>
         </is>
       </c>
     </row>
@@ -1947,46 +1947,46 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>career_growth</t>
+          <t>opportunities</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Career Growth</t>
+          <t>Opportunities</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>career_growth_2_choices</t>
+          <t>company_values_3_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>transparency</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Transparency</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>career_growth_2_choices</t>
+          <t>company_values_3_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>opportunities</t>
+          <t>openness</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Opportunities</t>
+          <t>Openness</t>
         </is>
       </c>
     </row>
@@ -1998,44 +1998,10 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>transparency</t>
+          <t>flexibility</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
-        <is>
-          <t>Transparency</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>company_values_3_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>openness</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Openness</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>company_values_3_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>flexibility</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
         <is>
           <t>Flexibility</t>
         </is>
